--- a/DesignTable/Data/Table/Tables/user_character.xlsx
+++ b/DesignTable/Data/Table/Tables/user_character.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EABC3F59-4B22-4646-8159-DAF79BF342A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F2A7838-30A3-4AC3-B824-C3C913E83CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-240" yWindow="0" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{4BB7BB50-360A-4F0A-A8DA-7C10F8C069F4}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4BB7BB50-360A-4F0A-A8DA-7C10F8C069F4}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
     <sheet name="verify" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>char_Id</t>
   </si>
   <si>
@@ -138,6 +134,14 @@
   </si>
   <si>
     <t>char_prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -195,7 +199,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -225,6 +233,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -246,7 +255,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="2" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="7" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -255,25 +264,25 @@
   <autoFilter ref="A1:G2" xr:uid="{6F11DBD4-B0B6-485C-B5F5-7E517590C911}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A1000B92-33C2-46D7-846C-1478477BAE43}" uniqueName="char_Id" name="char_Id">
-      <xmlColumnPr mapId="2" xpath="/user_character/record/char_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/record/char_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CCE3106F-36BF-480C-BFB1-60558EA78F7F}" uniqueName="char_classId" name="char_classId">
-      <xmlColumnPr mapId="2" xpath="/user_character/record/char_classId" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/record/char_classId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{027932CF-EB03-46DD-9870-599C33E71D19}" uniqueName="char_gender" name="char_gender">
-      <xmlColumnPr mapId="2" xpath="/user_character/record/char_gender" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/record/char_gender" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{F25EAF1C-D578-42B7-A0A2-C30574E9EE93}" uniqueName="char_atk" name="char_atk">
-      <xmlColumnPr mapId="2" xpath="/user_character/record/char_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/record/char_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{2D1814CD-D9EA-408B-8573-9E5FEAA44DB5}" uniqueName="char_def" name="char_def">
-      <xmlColumnPr mapId="2" xpath="/user_character/record/char_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/record/char_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{DC1CFE69-65C5-4AE1-AA4D-C1177C08AD7B}" uniqueName="char_moveSpeed" name="char_moveSpeed">
-      <xmlColumnPr mapId="2" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{AB5E937B-1662-4BD9-A68D-493B1CF2B005}" uniqueName="char_prefab" name="char_prefab">
-      <xmlColumnPr mapId="2" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -281,35 +290,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B7E07B84-A42D-4A7F-AE87-37DE018A9197}" name="표1" displayName="표1" ref="A1:I8" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I8" xr:uid="{B7E07B84-A42D-4A7F-AE87-37DE018A9197}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B7E07B84-A42D-4A7F-AE87-37DE018A9197}" name="표1" displayName="표1" ref="A1:J8" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J8" xr:uid="{B7E07B84-A42D-4A7F-AE87-37DE018A9197}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4DD28631-1EFD-48BF-B309-26618BF7886C}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{76CDE5E2-4AF5-4EF9-80B0-C7D7DA8DF5DA}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F08CF1A0-4129-40F0-848F-A8726645AD45}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{D5906E55-1ACD-48FC-93E6-B998E80DF15A}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{198743F0-82BC-4BCE-9FF6-D2E3431EE8FD}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{CAEB80B9-14BB-49FA-A7ED-A477E756342E}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1FA9E9E7-8BCE-498E-964B-AB1B6023C039}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{61BBF5EC-5050-463C-8B1E-80994AC3194B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{BAD4ADF8-31AC-4AF4-AADF-20732ED0641D}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="2" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{BAD4ADF8-31AC-4AF4-AADF-20732ED0641D}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{DF77AD38-3C93-442D-AC7A-8A15788BEB68}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="7" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -618,25 +630,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -659,10 +671,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E393F401-BC06-47A6-A16D-855C3F90918D}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -688,209 +700,233 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1011</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1">
         <v>1011</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1">
         <v>1011</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1">
         <v>1011</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="1">
         <v>1011</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="1">
         <v>1011</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="1">
         <v>1011</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/user_character.xlsx
+++ b/DesignTable/Data/Table/Tables/user_character.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F2A7838-30A3-4AC3-B824-C3C913E83CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AF595B3-40B3-4A8A-90A6-A8BE441C5C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4BB7BB50-360A-4F0A-A8DA-7C10F8C069F4}"/>
   </bookViews>
@@ -255,7 +255,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="7" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -264,25 +264,25 @@
   <autoFilter ref="A1:G2" xr:uid="{6F11DBD4-B0B6-485C-B5F5-7E517590C911}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A1000B92-33C2-46D7-846C-1478477BAE43}" uniqueName="char_Id" name="char_Id">
-      <xmlColumnPr mapId="7" xpath="/user_character/record/char_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/record/char_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CCE3106F-36BF-480C-BFB1-60558EA78F7F}" uniqueName="char_classId" name="char_classId">
-      <xmlColumnPr mapId="7" xpath="/user_character/record/char_classId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/record/char_classId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{027932CF-EB03-46DD-9870-599C33E71D19}" uniqueName="char_gender" name="char_gender">
-      <xmlColumnPr mapId="7" xpath="/user_character/record/char_gender" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/record/char_gender" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{F25EAF1C-D578-42B7-A0A2-C30574E9EE93}" uniqueName="char_atk" name="char_atk">
-      <xmlColumnPr mapId="7" xpath="/user_character/record/char_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/record/char_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{2D1814CD-D9EA-408B-8573-9E5FEAA44DB5}" uniqueName="char_def" name="char_def">
-      <xmlColumnPr mapId="7" xpath="/user_character/record/char_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/record/char_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{DC1CFE69-65C5-4AE1-AA4D-C1177C08AD7B}" uniqueName="char_moveSpeed" name="char_moveSpeed">
-      <xmlColumnPr mapId="7" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{AB5E937B-1662-4BD9-A68D-493B1CF2B005}" uniqueName="char_prefab" name="char_prefab">
-      <xmlColumnPr mapId="7" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -294,34 +294,34 @@
   <autoFilter ref="A1:J8" xr:uid="{B7E07B84-A42D-4A7F-AE87-37DE018A9197}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4DD28631-1EFD-48BF-B309-26618BF7886C}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{76CDE5E2-4AF5-4EF9-80B0-C7D7DA8DF5DA}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F08CF1A0-4129-40F0-848F-A8726645AD45}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{D5906E55-1ACD-48FC-93E6-B998E80DF15A}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{198743F0-82BC-4BCE-9FF6-D2E3431EE8FD}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{CAEB80B9-14BB-49FA-A7ED-A477E756342E}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1FA9E9E7-8BCE-498E-964B-AB1B6023C039}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{61BBF5EC-5050-463C-8B1E-80994AC3194B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{BAD4ADF8-31AC-4AF4-AADF-20732ED0641D}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{DF77AD38-3C93-442D-AC7A-8A15788BEB68}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="7" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/user_character.xlsx
+++ b/DesignTable/Data/Table/Tables/user_character.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AF595B3-40B3-4A8A-90A6-A8BE441C5C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{469E5B76-3CB3-4F80-B595-1E04F004636D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4BB7BB50-360A-4F0A-A8DA-7C10F8C069F4}"/>
   </bookViews>
@@ -255,7 +255,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="9" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="11" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -264,25 +264,25 @@
   <autoFilter ref="A1:G2" xr:uid="{6F11DBD4-B0B6-485C-B5F5-7E517590C911}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A1000B92-33C2-46D7-846C-1478477BAE43}" uniqueName="char_Id" name="char_Id">
-      <xmlColumnPr mapId="9" xpath="/user_character/record/char_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/record/char_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CCE3106F-36BF-480C-BFB1-60558EA78F7F}" uniqueName="char_classId" name="char_classId">
-      <xmlColumnPr mapId="9" xpath="/user_character/record/char_classId" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/record/char_classId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{027932CF-EB03-46DD-9870-599C33E71D19}" uniqueName="char_gender" name="char_gender">
-      <xmlColumnPr mapId="9" xpath="/user_character/record/char_gender" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/record/char_gender" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{F25EAF1C-D578-42B7-A0A2-C30574E9EE93}" uniqueName="char_atk" name="char_atk">
-      <xmlColumnPr mapId="9" xpath="/user_character/record/char_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/record/char_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{2D1814CD-D9EA-408B-8573-9E5FEAA44DB5}" uniqueName="char_def" name="char_def">
-      <xmlColumnPr mapId="9" xpath="/user_character/record/char_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/record/char_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{DC1CFE69-65C5-4AE1-AA4D-C1177C08AD7B}" uniqueName="char_moveSpeed" name="char_moveSpeed">
-      <xmlColumnPr mapId="9" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{AB5E937B-1662-4BD9-A68D-493B1CF2B005}" uniqueName="char_prefab" name="char_prefab">
-      <xmlColumnPr mapId="9" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -294,34 +294,34 @@
   <autoFilter ref="A1:J8" xr:uid="{B7E07B84-A42D-4A7F-AE87-37DE018A9197}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4DD28631-1EFD-48BF-B309-26618BF7886C}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{76CDE5E2-4AF5-4EF9-80B0-C7D7DA8DF5DA}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F08CF1A0-4129-40F0-848F-A8726645AD45}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{D5906E55-1ACD-48FC-93E6-B998E80DF15A}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{198743F0-82BC-4BCE-9FF6-D2E3431EE8FD}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{CAEB80B9-14BB-49FA-A7ED-A477E756342E}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1FA9E9E7-8BCE-498E-964B-AB1B6023C039}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{61BBF5EC-5050-463C-8B1E-80994AC3194B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{BAD4ADF8-31AC-4AF4-AADF-20732ED0641D}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{DF77AD38-3C93-442D-AC7A-8A15788BEB68}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="9" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/user_character.xlsx
+++ b/DesignTable/Data/Table/Tables/user_character.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{469E5B76-3CB3-4F80-B595-1E04F004636D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94E9D23F-D813-4B5C-9350-A786AA170B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4BB7BB50-360A-4F0A-A8DA-7C10F8C069F4}"/>
   </bookViews>
@@ -255,7 +255,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="11" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="12" Name="user_character_맵" RootElement="user_character" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -264,25 +264,25 @@
   <autoFilter ref="A1:G2" xr:uid="{6F11DBD4-B0B6-485C-B5F5-7E517590C911}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A1000B92-33C2-46D7-846C-1478477BAE43}" uniqueName="char_Id" name="char_Id">
-      <xmlColumnPr mapId="11" xpath="/user_character/record/char_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/record/char_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CCE3106F-36BF-480C-BFB1-60558EA78F7F}" uniqueName="char_classId" name="char_classId">
-      <xmlColumnPr mapId="11" xpath="/user_character/record/char_classId" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/record/char_classId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{027932CF-EB03-46DD-9870-599C33E71D19}" uniqueName="char_gender" name="char_gender">
-      <xmlColumnPr mapId="11" xpath="/user_character/record/char_gender" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/record/char_gender" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{F25EAF1C-D578-42B7-A0A2-C30574E9EE93}" uniqueName="char_atk" name="char_atk">
-      <xmlColumnPr mapId="11" xpath="/user_character/record/char_atk" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/record/char_atk" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{2D1814CD-D9EA-408B-8573-9E5FEAA44DB5}" uniqueName="char_def" name="char_def">
-      <xmlColumnPr mapId="11" xpath="/user_character/record/char_def" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/record/char_def" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{DC1CFE69-65C5-4AE1-AA4D-C1177C08AD7B}" uniqueName="char_moveSpeed" name="char_moveSpeed">
-      <xmlColumnPr mapId="11" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/record/char_moveSpeed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{AB5E937B-1662-4BD9-A68D-493B1CF2B005}" uniqueName="char_prefab" name="char_prefab">
-      <xmlColumnPr mapId="11" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/record/char_prefab" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -294,34 +294,34 @@
   <autoFilter ref="A1:J8" xr:uid="{B7E07B84-A42D-4A7F-AE87-37DE018A9197}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4DD28631-1EFD-48BF-B309-26618BF7886C}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{76CDE5E2-4AF5-4EF9-80B0-C7D7DA8DF5DA}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{F08CF1A0-4129-40F0-848F-A8726645AD45}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{D5906E55-1ACD-48FC-93E6-B998E80DF15A}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{198743F0-82BC-4BCE-9FF6-D2E3431EE8FD}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{CAEB80B9-14BB-49FA-A7ED-A477E756342E}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{1FA9E9E7-8BCE-498E-964B-AB1B6023C039}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{61BBF5EC-5050-463C-8B1E-80994AC3194B}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{BAD4ADF8-31AC-4AF4-AADF-20732ED0641D}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{DF77AD38-3C93-442D-AC7A-8A15788BEB68}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="11" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="12" xpath="/user_character/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
